--- a/daily_matches/job_matches_2026-05-19.xlsx
+++ b/daily_matches/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer (Onsite)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Rockland Trust Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Databricks</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b886774f2191937</t>
+          <t>https://www.indeed.com/viewjob?jk=26d4e78c9c5edc3b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BIBA Practice - Big Data Architect</t>
+          <t>GenAI &amp; Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Redshift, Docker, CI/CD, Terraform, Git, Redshift, PySpark, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering, FastAPI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a35842ddaad367b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c692fccbf68390f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Nexxen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, MySQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d474f9c4c5e446c7</t>
+          <t>https://www.indeed.com/viewjob?jk=295c684443aaf7cf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, PostgreSQL</t>
+          <t>RAG, S3, EC2, BigQuery, Kubernetes, Terraform, Git, Snowflake, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab39fae8644125cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d6423a9118a525a7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Integration Developer, Senior</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Uniti</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, XGBoost, Azure ML, Git, Snowflake, Matplotlib, Seaborn, Python</t>
+          <t>RAG, BigQuery, Synapse, CI/CD, GitHub Actions, Git, Snowflake, Databricks, BigQuery, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89e9f724a83d503</t>
+          <t>https://www.indeed.com/viewjob?jk=03b8bbec4a94a31c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pharma Applications Engineer</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Varda Space Industries</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, CI/CD, Git, Snowflake, Databricks, Redshift, Tableau, Power BI, Python, SQL</t>
+          <t>Data Scientist, CI/CD, Git, Snowflake, Databricks, PySpark, Hadoop, Tableau, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82dba2e1c1cad0d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebb5de3ed4f3c295</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11e647dbed7b5909</t>
+          <t>https://www.indeed.com/viewjob?jk=ac5da2405efac976</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (AI Software &amp; Operations)</t>
+          <t>Data Platform Architect, AI Adoption</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Elkridge, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, EC2, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Snowflake, Databricks, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e232fc0f23fb323</t>
+          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data and AI Quality Automation Engineer</t>
+          <t>Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stratus</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Snowflake, Databricks, Kafka, MySQL, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471e912481eed840</t>
+          <t>https://www.indeed.com/viewjob?jk=25ebdbd6c6149d6e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Enterprise AI Product Engineer</t>
+          <t>Sr. Software Engineer – Test Infrastructure &amp; Tooling</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RingCentral</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belmont, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Prompt Engineering, Git, PostgreSQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2182fa6e9ecd3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=37dfa6309a6d439e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Scientist</t>
+          <t>AI Engineer, Databricks</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>KeyLogic Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d43e4c373485181</t>
+          <t>https://www.indeed.com/viewjob?jk=d034a9b54566f452</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Agent Builder</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>MIRAKL SAS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Gemini, Mistral, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8e6b57611ebd179</t>
+          <t>https://www.indeed.com/viewjob?jk=ba21f68926acee84</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineering Intern New</t>
+          <t>Senior Software Engineer - Data Team (AWS, Flink, OpenSearch)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Podium</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, Kinesis, Kubernetes, Terraform, Git, Snowflake, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9bea0c93cdd60e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6243de26ae2262db</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Podium</t>
+          <t>Light &amp; Wonder</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5491f3f7e390427</t>
+          <t>https://www.indeed.com/viewjob?jk=30ff63fc363cb419</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer - Forward Deployed Engineer Â· Snowflake Â· Reinvention Centers</t>
+          <t>AI Applications Engineer Senior</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Logic, Inc.</t>
+          <t>Archrock</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Cortex, CI/CD, Terraform, Snowflake, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Synapse, Data Lake, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,42 +986,1232 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75881f342bf197d</t>
+          <t>https://www.indeed.com/viewjob?jk=4b623db6a37e3b69</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>MTSI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, MLflow, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd59b970d35a11e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr Data Analyst - Digital Ecommerce (Math/Stats, A/B testing, ML)(Remote Or Hybrid)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Hadoop, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c064401717f46f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Solana Mobile</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Solana Labs</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e51450b13e3da156</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineering MTS, Salesforce Developer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b0f3b16b4c8c825</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, AWS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Encova Insurance</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86454c96969d5666</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Engineer - Forward Deployed Engineer · Snowflake · Reinvention Centers</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Cortex, CI/CD, Terraform, Snowflake, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=041ab11f45c686fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Engineer - Forward Deployed Engineer · Snowflake · Reinvention Centers</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Cortex, CI/CD, Terraform, Snowflake, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d723ab9e0e74fcb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Engineer - Forward Deployed Engineer · Snowflake · Reinvention Centers</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Cortex, CI/CD, Terraform, Snowflake, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72dc14d6c481a779</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Engineer - Forward Deployed Engineer · Snowflake · Reinvention Centers</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Cortex, CI/CD, Terraform, Snowflake, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7058523ffe68aefb</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI Engineer - Forward Deployed Engineer · Snowflake · Reinvention Centers</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Cortex, CI/CD, Terraform, Snowflake, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92989df913f1d026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Red Cell Partners</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, S3, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=055f8e3ef195b4d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Penske Truck Leasing</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=566e62e913124271</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Experian</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=861f927e60b04e75</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer, Cloud - Next-Gen SIEM (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75cc105848b8bc60</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>eFileCabinet</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77c1681a932b7402</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Agentic AI Applications</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Serko Ltd</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd7b1b9e97d119f1</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Docker, CI/CD, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9341af6669f3e09</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Agentic AI Applications</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Serko Ltd</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Docker, CI/CD, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa130ba92e9c211b</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Agentic AI Applications</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Serko Ltd</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Docker, CI/CD, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58f4f2a47e666c5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Agentic AI Applications</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Serko Ltd</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Docker, CI/CD, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfc0e2b7e2150900</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Application Architect</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Zelis Healthcare</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfaab26038413c27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Light &amp; Wonder</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, AKS, CI/CD, Snowflake, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7d4a95f99fd78e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer-Junior</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>General Dynamics Information Technology</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d7388470b002f26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CCC Intelligent Solutions</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Docker, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fe4964f59934fcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Junior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MTSI</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>MLflow, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d30e5165de2999c</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MTSI</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MLflow, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fe38a974a578c18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>IT Platform Engineer-Analytics Services</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Mi-Wuk Village, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Git, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1c3f9ecedf8af84</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Savvas Learning Company</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec50b6ac6654c9d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Savvas Learning Company</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7e0de41e25c62b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Savvas Learning Company</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fabee5cab6d4fc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Savvas Learning Company</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c4dfa91274edf2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Savvas Learning Company</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00e18673bd4e6166</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Savvas Learning Company</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e148a42c2439dc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Harbor Freight Tools</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Calabasas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, CI/CD, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16ad4bea460aef83</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Engineer (Node.js, Python, Go, Azure)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Lenovo</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a697aaa5d0d3ecff</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Forward Deployment Engineer-AI</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cyclotron</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=038da72b1e8aae77</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-19.xlsx
+++ b/daily_matches/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>TCPWave</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4ce7bf4011426a</t>
+          <t>https://www.indeed.com/viewjob?jk=3aa550f557c45270</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern</t>
+          <t>Data Engineer- Local</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PlusAI</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Mistral, Hugging Face, FAISS, Prompt Engineering, NoSQL, Python</t>
+          <t>Data Scientist, S3, EC2, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc3f75cb6e558527</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern - Data Infrastructure and Tools</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PlusAI</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, AKS, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a158d64aed7cba7</t>
+          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevSecOps / Security Engineer – Application &amp; Cloud (Ecommerce)</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thorne</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Terraform, Git, NoSQL, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,137 +601,137 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f7be3e52d3af700</t>
+          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charta Health</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17956a2d4c5efe6a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer, Senior</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Charta Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Git, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63023cca7ec2453c</t>
+          <t>https://www.indeed.com/viewjob?jk=88dfefca6da19496</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Platform Specialist</t>
+          <t>Data Scientist - Modeling and Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PAE Consulting Engineers Inc.</t>
+          <t>AAA Life Insurance Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, Hadoop, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,137 +741,137 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9fc7f0b5658d616</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d0a381b86783c0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Sr. Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KLS Martin Group</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, MLflow, FastAPI, AKS, CI/CD, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bea993a31bcad7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f33e808282854416</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Calqulate</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, PyTorch, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f5af68d7a33b2d</t>
+          <t>https://www.indeed.com/viewjob?jk=429cbcb1d198da00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Computational Linguist, Generative AI - Sr. Associate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, BigQuery, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, NLTK, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034ae52b91d558d2</t>
+          <t>https://www.indeed.com/viewjob?jk=83bfded0ccc1a8c2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CPMC LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, S3, Snowflake, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, AKS, CI/CD, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6fa2bd91cdba2d</t>
+          <t>https://www.indeed.com/viewjob?jk=a8b83278154c4cae</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>POINT C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994c9adb9c90bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=801e2eb007094721</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI &amp; ML Engineer</t>
+          <t>Sr Engineer, Data Science &amp; Machine Learning Operations - remote opportunity</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Tivity Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,52 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, AWS SageMaker, Snowflake, Hadoop, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, Glue, Data Lake, CI/CD, Terraform, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21631dfcc377b420</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>DEPLOY</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9592ae4077ed5bb1</t>
+          <t>https://www.indeed.com/viewjob?jk=1ba5979330da050e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-19.xlsx
+++ b/daily_matches/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>.NET Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TCPWave</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa550f557c45270</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e4611f2709de72</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Git</t>
+          <t>RAG, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Data Analyst - ALM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake, BigQuery, Redshift, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
+          <t>https://www.indeed.com/viewjob?jk=bf376fb80f5f02f9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior AI &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Alamar Biosciences</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, BigQuery, Data Lake, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
+          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Gen II Fund Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
+          <t>https://www.indeed.com/viewjob?jk=09721a45d1504bfd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Solution Engineer: Enterprise GenAI &amp; Analytics Enablement</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, MLflow, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=9df419a67df1ba59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Intregration Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>IntegraTouch</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Git, Databricks, BigQuery</t>
+          <t>RAG, S3, Docker, Kubernetes, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,137 +706,137 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88dfefca6da19496</t>
+          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist - Modeling and Analytics</t>
+          <t>Senior Full Stack Product Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AAA Life Insurance Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>India Hook, SC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, Hadoop, Tableau, Power BI, Python, SQL</t>
+          <t>AI Engineer, RAG, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d0a381b86783c0</t>
+          <t>https://www.indeed.com/viewjob?jk=a62b4aca50c54501</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Artificial Intelligence Engineer</t>
+          <t>Database Administrator (New York, NY - US)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Energy Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, Git, Python</t>
+          <t>Generative AI, PostgreSQL, MySQL, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f33e808282854416</t>
+          <t>https://www.indeed.com/viewjob?jk=6d13c0f429a80b43</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Database Administrator (Portland, OR - US)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Energy Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, Git, Python</t>
+          <t>Generative AI, PostgreSQL, MySQL, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429cbcb1d198da00</t>
+          <t>https://www.indeed.com/viewjob?jk=1df1dc65f5bf751b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Computational Linguist, Generative AI - Sr. Associate</t>
+          <t>Database Administrator (Chicago, IL- US)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Energy Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, NLTK, Git, Python, R</t>
+          <t>Generative AI, PostgreSQL, MySQL, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83bfded0ccc1a8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=cb65af8c43f9fc32</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Database Administrator (Orange, CA - US)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CPMC LLC</t>
+          <t>Energy Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Docker, Kubernetes, AKS, CI/CD, Python, R, Optimization</t>
+          <t>Generative AI, PostgreSQL, MySQL, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8b83278154c4cae</t>
+          <t>https://www.indeed.com/viewjob?jk=505e60955729c7b6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Database Administrator (Boston,MA - US)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>POINT C</t>
+          <t>Energy Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, SQL, R, Java, Scala</t>
+          <t>Generative AI, PostgreSQL, MySQL, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,182 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801e2eb007094721</t>
+          <t>https://www.indeed.com/viewjob?jk=21538c437c55ec26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Science &amp; Machine Learning Operations - remote opportunity</t>
+          <t>Database Administrator (Oakland, CA - US)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tivity Health</t>
+          <t>Energy Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, PostgreSQL, MySQL, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cadff332c22c58a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer, Online Decisioning</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Signifyd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Databricks, Cassandra, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce22b6e467b204eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Scientist - GenAI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Wellesley, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FastAPI, Docker, Jenkins, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1482aca9e8fe5ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Scientist - GenAI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FastAPI, Docker, Jenkins, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7a4f8cda0f144f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Platform AI Engineers</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CLOUDSUFI</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, Data Lake, CI/CD, Terraform, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ba5979330da050e</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, BigQuery, CI/CD, Terraform, Git, BigQuery, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4956977f1dd7c4f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-19.xlsx
+++ b/daily_matches/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>.NET Architect</t>
+          <t>Data &amp; Analytics Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>L.E.K. Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, NoSQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, GCP Vertex AI, Redshift, BigQuery, Data Lake, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e4611f2709de72</t>
+          <t>https://www.indeed.com/viewjob?jk=9ddcbcd3fcf90b62</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Full Stack Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>WeZON USA, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Databricks</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
+          <t>https://www.indeed.com/viewjob?jk=a882055d51c01beb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - ALM</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake, BigQuery, Redshift, PostgreSQL</t>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf376fb80f5f02f9</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alamar Biosciences</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,182 +591,182 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, BigQuery, Data Lake, Snowflake, Databricks</t>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
+          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gen II Fund Services</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09721a45d1504bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Solution Engineer: Enterprise GenAI &amp; Analytics Enablement</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9df419a67df1ba59</t>
+          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Intregration Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IntegraTouch</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
+          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Product Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Hook, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java</t>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a62b4aca50c54501</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Database Administrator (New York, NY - US)</t>
+          <t>Python AI Developer with RAG and Azure and Agentic AI - (W2 position)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Energy Solutions</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, PostgreSQL, MySQL, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, FAISS, Pinecone, ChromaDB, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d13c0f429a80b43</t>
+          <t>https://www.indeed.com/viewjob?jk=49ee26cd7f4c82f5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Database Administrator (Portland, OR - US)</t>
+          <t>Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energy Solutions</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, PostgreSQL, MySQL, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,207 +811,207 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df1dc65f5bf751b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0a02abf6d37a858</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Database Administrator (Chicago, IL- US)</t>
+          <t>Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energy Solutions</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, PostgreSQL, MySQL, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb65af8c43f9fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=46db9aa4e2f0b8f6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Database Administrator (Orange, CA - US)</t>
+          <t>Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energy Solutions</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, PostgreSQL, MySQL, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=505e60955729c7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=c8a25e083e345b6b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Database Administrator (Boston,MA - US)</t>
+          <t>Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Energy Solutions</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, PostgreSQL, MySQL, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21538c437c55ec26</t>
+          <t>https://www.indeed.com/viewjob?jk=e56141200d809b90</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Database Administrator (Oakland, CA - US)</t>
+          <t>Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Energy Solutions</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, PostgreSQL, MySQL, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cadff332c22c58a9</t>
+          <t>https://www.indeed.com/viewjob?jk=acbee22ead236be6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer, Online Decisioning</t>
+          <t>Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Signifyd</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Databricks, Cassandra, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce22b6e467b204eb</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd68611435c0c03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist - GenAI</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>skyline career</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FastAPI, Docker, Jenkins, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1482aca9e8fe5ca</t>
+          <t>https://www.indeed.com/viewjob?jk=30f07c5b6836e11b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist - GenAI</t>
+          <t>AI and ML Platforms QA Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FastAPI, Docker, Jenkins, Python, R, Scala</t>
+          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Snowflake, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,217 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7a4f8cda0f144f3</t>
+          <t>https://www.indeed.com/viewjob?jk=edc6b17224894e0a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Platform AI Engineers</t>
+          <t>AI / ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLOUDSUFI</t>
+          <t>AssetWorks</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Wayne, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4c4b5e3a05c6dab</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr Machine Learning Engineer, Adobe Firefly Services</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7c114955d9e73b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AeroVironment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Germantown, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, Keras, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21173c8a67078895</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior GIS Data Analyst (Utilities)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MCKIM &amp; CREED</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, BigQuery, CI/CD, Terraform, Git, BigQuery, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Power BI, Matplotlib, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4956977f1dd7c4f</t>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f01a8715268de52</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pillar4 Media</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Git, Power BI, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b0d9ab802632c41</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Search and Recommendations</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CarMax</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Databricks, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbd8eb1968c012b9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-19.xlsx
+++ b/daily_matches/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Senior Data Engineer</t>
+          <t>R-02 Claude Enterprise Agentic AI Ecosystem Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L.E.K. Consulting</t>
+          <t>Ariana.Digital</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, GCP Vertex AI, Redshift, BigQuery, Data Lake, FastAPI</t>
+          <t>Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddcbcd3fcf90b62</t>
+          <t>https://www.indeed.com/viewjob?jk=afbf42b41177cad5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Full Stack Developer</t>
+          <t>AI Full Stack Developer / Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WeZON USA, Inc.</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a882055d51c01beb</t>
+          <t>https://www.indeed.com/viewjob?jk=9a74366c8261121c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>AI Full Stack Developer &amp; Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, Git, Kafka, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,207 +566,207 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
+          <t>https://www.indeed.com/viewjob?jk=02d8b70229d05089</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Forward Deployed Engineer (Foundry)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Trinity Industries</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, Git, Kafka, PostgreSQL</t>
+          <t>RAG, TensorFlow, PyTorch, CI/CD, Snowflake, Databricks, PySpark, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1207216093eb19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Scientist 100% Remote – Must be US Citizen due to Public Trust Clearance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Cypress Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, Git, Kafka, PostgreSQL</t>
+          <t>Data Scientist, Databricks, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=eb7e89b58a306f8e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, Git, Kafka, PostgreSQL</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Keras, Azure ML, Snowflake, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a0a268763c712eb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Scientist - Clinical AI development</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Novo Nordisk, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Lexington, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, Git, Kafka, PostgreSQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, CI/CD, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9b75aacf0700b3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, Git, Kafka, PostgreSQL</t>
+          <t>RAG, Copilot, Synapse, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python AI Developer with RAG and Azure and Agentic AI - (W2 position)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Syncreon Consulting</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FAISS, Pinecone, ChromaDB, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ee26cd7f4c82f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6ada032bb43ae458</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack AI Product Engineer</t>
+          <t>#22545 - Test Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,462 +811,112 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0a02abf6d37a858</t>
+          <t>https://www.indeed.com/viewjob?jk=2584f4866a2ce9f1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack AI Product Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
+          <t>RAG, S3, BigQuery, FastAPI, BigQuery, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46db9aa4e2f0b8f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack AI Product Engineer</t>
+          <t>AI Integrator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Jet Industries</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
+          <t>RAG, TensorFlow, PyTorch, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8a25e083e345b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=36480a676227c3bc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack AI Product Engineer</t>
+          <t>Home Loans Loss Forecasting Analytics, Senior Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
+          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56141200d809b90</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Full Stack AI Product Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Bain &amp; Company</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=acbee22ead236be6</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Full Stack AI Product Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Bain &amp; Company</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd68611435c0c03</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>skyline career</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Hadoop, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30f07c5b6836e11b</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AI and ML Platforms QA Engineer III</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ICW Group</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Snowflake, SQL, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edc6b17224894e0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AI / ML Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>AssetWorks</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Wayne, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c4b5e3a05c6dab</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Sr Machine Learning Engineer, Adobe Firefly Services</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Kubernetes, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c114955d9e73b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineering Intern</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>AeroVironment</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Germantown, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, Keras, Git, Python, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21173c8a67078895</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior GIS Data Analyst (Utilities)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>MCKIM &amp; CREED</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Power BI, Matplotlib, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f01a8715268de52</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Pillar4 Media</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Git, Power BI, Python, SQL, R, Scala, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0d9ab802632c41</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Search and Recommendations</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>CarMax</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Databricks, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbd8eb1968c012b9</t>
+          <t>https://www.indeed.com/viewjob?jk=dea4ebb7b98f7326</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-19.xlsx
+++ b/daily_matches/job_matches_2026-05-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R-02 Claude Enterprise Agentic AI Ecosystem Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ariana.Digital</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, S3, EC2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbf42b41177cad5</t>
+          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Full Stack Developer / Architect</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, NoSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, S3, EC2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a74366c8261121c</t>
+          <t>https://www.indeed.com/viewjob?jk=746360ee3987922f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Full Stack Developer &amp; Architect</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sbt Global</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, NoSQL</t>
+          <t>Cortex, Glue, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Tableau, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d8b70229d05089</t>
+          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Forward Deployed Engineer (Foundry)</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trinity Industries</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, CI/CD, Snowflake, Databricks, PySpark, Tableau, Python, SQL</t>
+          <t>Cortex, Glue, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Tableau, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1207216093eb19</t>
+          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist 100% Remote – Must be US Citizen due to Public Trust Clearance</t>
+          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cypress Consulting</t>
+          <t>Bedrock Data</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Databricks, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
+          <t>RAG, Data Lake, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb7e89b58a306f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Revenue Strategy Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>AfterShip</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Keras, Azure ML, Snowflake, Databricks, PySpark, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a0a268763c712eb</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac0e0c87e87423f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Clinical AI development</t>
+          <t>Revenue Strategy Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Novo Nordisk, Inc.</t>
+          <t>AfterShip</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lexington, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, PyTorch, CI/CD, Python, R, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9b75aacf0700b3</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe206fd1918b8d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
+          <t>https://www.indeed.com/viewjob?jk=b591868fadbb51ae</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ada032bb43ae458</t>
+          <t>https://www.indeed.com/viewjob?jk=938bdf4b7c9d1253</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>#22545 - Test Architect</t>
+          <t>Software Developer - Virtualization and SIL Integration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala, Optimization</t>
+          <t>RAG, FastAPI, CI/CD, Jenkins, Git, PostgreSQL, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2584f4866a2ce9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=fcc80ac63e72b991</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Azure Data Engineer (Telecommunications)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, BigQuery, FastAPI, BigQuery, Kafka, Python, R, Scala</t>
+          <t>Copilot, CI/CD, Git, Snowflake, Databricks, PySpark, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
+          <t>https://www.indeed.com/viewjob?jk=3b6f172e62819712</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Integrator</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jet Industries</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,42 +881,357 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36480a676227c3bc</t>
+          <t>https://www.indeed.com/viewjob?jk=80881e346cc6bf71</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Home Loans Loss Forecasting Analytics, Senior Data Scientist</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35cc8cff76f43f76</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Analyst - Data Engineering 5A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0b16d3b43103074</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93957a543e18fd69</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Semantic Data and AI Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Enterprise Knowledge</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>10</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dea4ebb7b98f7326</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Docker, Kubernetes, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18298b98a9b5b7d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Family Dollar</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chesapeake, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8dec169c8f48f3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Family Dollar</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chesapeake, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea6e89845a83c508</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer, Vehicle Identification</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BLISSWAY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, OpenCV, FastAPI, Docker, PostgreSQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6152efca5918a306</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Assembly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BLISSWAY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, OpenCV, FastAPI, Docker, PostgreSQL, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=560f7f322ba7a234</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer IV – AI &amp; Data Products</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Acima Leasing</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Copilot, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95f67a199a0b8bdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Data Science</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GPS Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Tableau, Python, SQL, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=301f442e774d294e</t>
         </is>
       </c>
     </row>
